--- a/artfynd/A 29122-2026 artfynd.xlsx
+++ b/artfynd/A 29122-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134951997</v>
+        <v>135250790</v>
       </c>
       <c r="B2" t="n">
-        <v>79131</v>
+        <v>79373</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>448180</v>
+        <v>448213</v>
       </c>
       <c r="R2" t="n">
-        <v>6753651</v>
+        <v>6753591</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,22 +749,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,7 +791,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134952371</v>
+        <v>134951997</v>
       </c>
       <c r="B3" t="n">
         <v>79131</v>
@@ -821,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>448191</v>
+        <v>448180</v>
       </c>
       <c r="R3" t="n">
-        <v>6753627</v>
+        <v>6753651</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,7 +907,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134952452</v>
+        <v>134952371</v>
       </c>
       <c r="B4" t="n">
         <v>79131</v>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>448221</v>
+        <v>448191</v>
       </c>
       <c r="R4" t="n">
-        <v>6753630</v>
+        <v>6753627</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -986,7 +986,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,7 +1023,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134952656</v>
+        <v>134952452</v>
       </c>
       <c r="B5" t="n">
         <v>79131</v>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1067,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>448222</v>
+        <v>448221</v>
       </c>
       <c r="R5" t="n">
-        <v>6753672</v>
+        <v>6753630</v>
       </c>
       <c r="S5" t="n">
         <v>2</v>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,6 +1136,238 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>134952656</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Vällbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>448222</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6753672</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>17:49</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>17:49</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135251072</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Vällbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>448194</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6753610</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29122-2026 artfynd.xlsx
+++ b/artfynd/A 29122-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135250790</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134951997</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134952371</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1136,6 +1156,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134952452</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1252,6 +1277,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134952656</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1368,8 +1398,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251072</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 29122-2026 artfynd.xlsx
+++ b/artfynd/A 29122-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135250790</v>
       </c>
       <c r="B2" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>134951997</v>
       </c>
       <c r="B3" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>134952371</v>
       </c>
       <c r="B4" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>134952452</v>
       </c>
       <c r="B5" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>134952656</v>
       </c>
       <c r="B6" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>135251072</v>
       </c>
       <c r="B7" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 29122-2026 artfynd.xlsx
+++ b/artfynd/A 29122-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135250790</v>
       </c>
       <c r="B2" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>135251072</v>
       </c>
       <c r="B7" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 29122-2026 artfynd.xlsx
+++ b/artfynd/A 29122-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,37 +680,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134951997</v>
+        <v>135250790</v>
       </c>
       <c r="B2" t="n">
-        <v>79169</v>
+        <v>79441</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>448180</v>
+        <v>448213</v>
       </c>
       <c r="R2" t="n">
-        <v>6753651</v>
+        <v>6753591</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,22 +754,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,13 +795,13 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134951997</t>
+          <t>https://artportalen.se/Sighting/135250790</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134952371</v>
+        <v>134951997</v>
       </c>
       <c r="B3" t="n">
         <v>79169</v>
@@ -831,7 +831,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -845,13 +845,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>448191</v>
+        <v>448180</v>
       </c>
       <c r="R3" t="n">
-        <v>6753627</v>
+        <v>6753651</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,13 +916,13 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134952371</t>
+          <t>https://artportalen.se/Sighting/134951997</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134952452</v>
+        <v>134952371</v>
       </c>
       <c r="B4" t="n">
         <v>79169</v>
@@ -966,10 +966,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>448221</v>
+        <v>448191</v>
       </c>
       <c r="R4" t="n">
-        <v>6753630</v>
+        <v>6753627</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,13 +1037,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134952452</t>
+          <t>https://artportalen.se/Sighting/134952371</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134952656</v>
+        <v>134952452</v>
       </c>
       <c r="B5" t="n">
         <v>79169</v>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>448222</v>
+        <v>448221</v>
       </c>
       <c r="R5" t="n">
-        <v>6753672</v>
+        <v>6753630</v>
       </c>
       <c r="S5" t="n">
         <v>2</v>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1158,7 +1158,249 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/134952452</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>134952656</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79169</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Vällbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>448222</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6753672</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>17:49</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>17:49</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/134952656</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135251072</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Vällbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>448194</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6753610</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251072</t>
         </is>
       </c>
     </row>
@@ -1168,6 +1410,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29122-2026 artfynd.xlsx
+++ b/artfynd/A 29122-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -801,57 +801,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134951997</v>
+        <v>135998305</v>
       </c>
       <c r="B3" t="n">
-        <v>79169</v>
+        <v>8463</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vällbäcken, Dlr</t>
+          <t>Solbodarna 1, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>448180</v>
+        <v>448153</v>
       </c>
       <c r="R3" t="n">
-        <v>6753651</v>
+        <v>6753542</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,22 +866,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,63 +907,54 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134951997</t>
+          <t>https://artportalen.se/Sighting/135998305</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134952371</v>
+        <v>135998301</v>
       </c>
       <c r="B4" t="n">
-        <v>79169</v>
+        <v>98157</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>221946</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vällbäcken, Dlr</t>
+          <t>Solbodarna 1, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>448191</v>
+        <v>448171</v>
       </c>
       <c r="R4" t="n">
-        <v>6753627</v>
+        <v>6753616</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -996,22 +978,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,13 +1019,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134952371</t>
+          <t>https://artportalen.se/Sighting/135998301</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134952452</v>
+        <v>134951997</v>
       </c>
       <c r="B5" t="n">
         <v>79169</v>
@@ -1073,7 +1055,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1087,13 +1069,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>448221</v>
+        <v>448180</v>
       </c>
       <c r="R5" t="n">
-        <v>6753630</v>
+        <v>6753651</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1122,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1132,7 +1114,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1158,13 +1140,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134952452</t>
+          <t>https://artportalen.se/Sighting/134951997</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134952656</v>
+        <v>134952371</v>
       </c>
       <c r="B6" t="n">
         <v>79169</v>
@@ -1194,7 +1176,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1208,10 +1190,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>448222</v>
+        <v>448191</v>
       </c>
       <c r="R6" t="n">
-        <v>6753672</v>
+        <v>6753627</v>
       </c>
       <c r="S6" t="n">
         <v>2</v>
@@ -1243,7 +1225,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1253,7 +1235,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1279,16 +1261,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134952656</t>
+          <t>https://artportalen.se/Sighting/134952371</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135251072</v>
+        <v>134952452</v>
       </c>
       <c r="B7" t="n">
-        <v>79199</v>
+        <v>79169</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1329,10 +1311,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>448194</v>
+        <v>448221</v>
       </c>
       <c r="R7" t="n">
-        <v>6753610</v>
+        <v>6753630</v>
       </c>
       <c r="S7" t="n">
         <v>2</v>
@@ -1359,22 +1341,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1400,7 +1382,585 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/134952452</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>134952656</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79169</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Vällbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>448222</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6753672</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>17:49</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>17:49</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134952656</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135251072</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Vällbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>448194</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6753610</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/135251072</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135998300</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79201</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Solbodarna 1, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>448250</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6753630</v>
+      </c>
+      <c r="S10" t="n">
+        <v>9</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135998300</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135998302</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79201</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Solbodarna 1, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>448181</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6753627</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135998302</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135998303</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79201</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Solbodarna 1, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>448178</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6753651</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135998303</t>
         </is>
       </c>
     </row>
@@ -1412,6 +1972,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29122-2026 artfynd.xlsx
+++ b/artfynd/A 29122-2026 artfynd.xlsx
@@ -916,7 +916,7 @@
         <v>135998301</v>
       </c>
       <c r="B4" t="n">
-        <v>98157</v>
+        <v>98158</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 29122-2026 artfynd.xlsx
+++ b/artfynd/A 29122-2026 artfynd.xlsx
@@ -916,7 +916,7 @@
         <v>135998301</v>
       </c>
       <c r="B4" t="n">
-        <v>98158</v>
+        <v>98159</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>135998300</v>
       </c>
       <c r="B10" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>135998302</v>
       </c>
       <c r="B11" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>135998303</v>
       </c>
       <c r="B12" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 29122-2026 artfynd.xlsx
+++ b/artfynd/A 29122-2026 artfynd.xlsx
@@ -916,7 +916,7 @@
         <v>135998301</v>
       </c>
       <c r="B4" t="n">
-        <v>98159</v>
+        <v>98160</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 29122-2026 artfynd.xlsx
+++ b/artfynd/A 29122-2026 artfynd.xlsx
@@ -916,7 +916,7 @@
         <v>135998301</v>
       </c>
       <c r="B4" t="n">
-        <v>98160</v>
+        <v>98161</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>135998300</v>
       </c>
       <c r="B10" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>135998302</v>
       </c>
       <c r="B11" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>135998303</v>
       </c>
       <c r="B12" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 29122-2026 artfynd.xlsx
+++ b/artfynd/A 29122-2026 artfynd.xlsx
@@ -916,7 +916,7 @@
         <v>135998301</v>
       </c>
       <c r="B4" t="n">
-        <v>98161</v>
+        <v>98167</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>135998300</v>
       </c>
       <c r="B10" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>135998302</v>
       </c>
       <c r="B11" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>135998303</v>
       </c>
       <c r="B12" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 29122-2026 artfynd.xlsx
+++ b/artfynd/A 29122-2026 artfynd.xlsx
@@ -916,7 +916,7 @@
         <v>135998301</v>
       </c>
       <c r="B4" t="n">
-        <v>98167</v>
+        <v>98168</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>135998300</v>
       </c>
       <c r="B10" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>135998302</v>
       </c>
       <c r="B11" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>135998303</v>
       </c>
       <c r="B12" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
